--- a/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
@@ -1,58 +1,582 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="61">
+  <si>
+    <t>MonsterId</t>
+  </si>
+  <si>
+    <t>ModelId</t>
+  </si>
+  <si>
+    <t>DisplayName</t>
+  </si>
+  <si>
+    <t>TargetSelect</t>
+  </si>
+  <si>
+    <t>AttackMode</t>
+  </si>
+  <si>
+    <t>MaxHP</t>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
+  </si>
+  <si>
+    <t>AttackPower</t>
+  </si>
+  <si>
+    <t>AttackSpeed</t>
+  </si>
+  <si>
+    <t>AttackRange</t>
+  </si>
+  <si>
+    <t>MeleeWindupSeconds</t>
+  </si>
+  <si>
+    <t>RangedProjectileSpeed</t>
+  </si>
+  <si>
+    <t>RangedTimeoutSeconds</t>
+  </si>
+  <si>
+    <t>Skills</t>
+  </si>
+  <si>
+    <t>LootDrop</t>
+  </si>
+  <si>
+    <t>Monster_01</t>
+  </si>
+  <si>
+    <t>MonsterModel_01</t>
+  </si>
+  <si>
+    <t>腐尸</t>
+  </si>
+  <si>
+    <t>Nearest</t>
+  </si>
+  <si>
+    <t>Melee</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Iron_1|Spirit_5</t>
+  </si>
+  <si>
+    <t>Monster_02</t>
+  </si>
+  <si>
+    <t>MonsterModel_02</t>
+  </si>
+  <si>
+    <t>骷髅兵</t>
+  </si>
+  <si>
+    <t>PreferWarrior</t>
+  </si>
+  <si>
+    <t>Ranged</t>
+  </si>
+  <si>
+    <t>Bone_1|Spirit_4</t>
+  </si>
+  <si>
+    <t>Monster_03</t>
+  </si>
+  <si>
+    <t>MonsterModel_03</t>
+  </si>
+  <si>
+    <t>墓园犬</t>
+  </si>
+  <si>
+    <t>PreferProtagonist</t>
+  </si>
+  <si>
+    <t>Iron_3|Spirit_7</t>
+  </si>
+  <si>
+    <t>Monster_04</t>
+  </si>
+  <si>
+    <t>MonsterModel_04</t>
+  </si>
+  <si>
+    <t>幽魂</t>
+  </si>
+  <si>
+    <t>Bone_1|Spirit_6</t>
+  </si>
+  <si>
+    <t>Monster_05</t>
+  </si>
+  <si>
+    <t>MonsterModel_05</t>
+  </si>
+  <si>
+    <t>石像鬼</t>
+  </si>
+  <si>
+    <t>Iron_2|Spirit_9</t>
+  </si>
+  <si>
+    <t>Monster_06</t>
+  </si>
+  <si>
+    <t>MonsterModel_06</t>
+  </si>
+  <si>
+    <t>巫妖徒</t>
+  </si>
+  <si>
+    <t>Bone_1|Spirit_8</t>
+  </si>
+  <si>
+    <t>Monster_07</t>
+  </si>
+  <si>
+    <t>MonsterModel_07</t>
+  </si>
+  <si>
+    <t>骨龙幼崽</t>
+  </si>
+  <si>
+    <t>Iron_1|Spirit_11</t>
+  </si>
+  <si>
+    <t>Monster_08</t>
+  </si>
+  <si>
+    <t>MonsterModel_08</t>
+  </si>
+  <si>
+    <t>血仆</t>
+  </si>
+  <si>
+    <t>Bone_1|Spirit_10</t>
+  </si>
+  <si>
+    <t>Monster_09</t>
+  </si>
+  <si>
+    <t>MonsterModel_09</t>
+  </si>
+  <si>
+    <t>暗影刺客</t>
+  </si>
+  <si>
+    <t>Iron_3|Spirit_13</t>
+  </si>
+  <si>
+    <t>Monster_10</t>
+  </si>
+  <si>
+    <t>MonsterModel_10</t>
+  </si>
+  <si>
+    <t>巨型僵尸</t>
+  </si>
+  <si>
+    <t>Bone_1|Spirit_12</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -60,18 +584,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -391,82 +1209,83 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>MonsterId</v>
-      </c>
-      <c r="B1" t="str">
-        <v>ModelId</v>
-      </c>
-      <c r="C1" t="str">
-        <v>DisplayName</v>
-      </c>
-      <c r="D1" t="str">
-        <v>TargetSelect</v>
-      </c>
-      <c r="E1" t="str">
-        <v>AttackMode</v>
-      </c>
-      <c r="F1" t="str">
-        <v>MaxHP</v>
-      </c>
-      <c r="G1" t="str">
-        <v>MoveSpeed</v>
-      </c>
-      <c r="H1" t="str">
-        <v>AttackPower</v>
-      </c>
-      <c r="I1" t="str">
-        <v>AttackSpeed</v>
-      </c>
-      <c r="J1" t="str">
-        <v>AttackRange</v>
-      </c>
-      <c r="K1" t="str">
-        <v>MeleeWindupSeconds</v>
-      </c>
-      <c r="L1" t="str">
-        <v>RangedProjectileSpeed</v>
-      </c>
-      <c r="M1" t="str">
-        <v>RangedTimeoutSeconds</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Skills</v>
-      </c>
-      <c r="O1" t="str">
-        <v>LootDrop</v>
+    <row r="1" spans="1:15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Monster_01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>MonsterModel_01</v>
-      </c>
-      <c r="C2" t="str">
-        <v>腐尸</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Nearest</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Melee</v>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
       </c>
       <c r="F2">
         <v>80</v>
       </c>
       <c r="G2">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
         <v>8</v>
@@ -475,7 +1294,7 @@
         <v>0.8</v>
       </c>
       <c r="J2">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="K2">
         <v>0.3</v>
@@ -486,34 +1305,34 @@
       <c r="M2">
         <v>0</v>
       </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v>Iron_1|Spirit_5</v>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Monster_02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>MonsterModel_02</v>
-      </c>
-      <c r="C3" t="str">
-        <v>骷髅兵</v>
-      </c>
-      <c r="D3" t="str">
-        <v>PreferWarrior</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Ranged</v>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
       </c>
       <c r="F3">
         <v>120</v>
       </c>
       <c r="G3">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
         <v>10</v>
@@ -522,7 +1341,7 @@
         <v>0.85</v>
       </c>
       <c r="J3">
-        <v>6.3</v>
+        <v>0.25</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -533,34 +1352,34 @@
       <c r="M3">
         <v>2.5</v>
       </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v>Bone_1|Spirit_4</v>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Monster_03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>MonsterModel_03</v>
-      </c>
-      <c r="C4" t="str">
-        <v>墓园犬</v>
-      </c>
-      <c r="D4" t="str">
-        <v>PreferProtagonist</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Melee</v>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
       </c>
       <c r="F4">
         <v>160</v>
       </c>
       <c r="G4">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="H4">
         <v>12</v>
@@ -569,7 +1388,7 @@
         <v>0.9</v>
       </c>
       <c r="J4">
-        <v>1.7</v>
+        <v>0.25</v>
       </c>
       <c r="K4">
         <v>0.34</v>
@@ -580,34 +1399,34 @@
       <c r="M4">
         <v>0</v>
       </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v>Iron_3|Spirit_7</v>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Monster_04</v>
-      </c>
-      <c r="B5" t="str">
-        <v>MonsterModel_04</v>
-      </c>
-      <c r="C5" t="str">
-        <v>幽魂</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Nearest</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Melee</v>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
       </c>
       <c r="F5">
         <v>200</v>
       </c>
       <c r="G5">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="H5">
         <v>14</v>
@@ -616,7 +1435,7 @@
         <v>0.95</v>
       </c>
       <c r="J5">
-        <v>1.8</v>
+        <v>0.25</v>
       </c>
       <c r="K5">
         <v>0.36</v>
@@ -627,34 +1446,34 @@
       <c r="M5">
         <v>0</v>
       </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v>Bone_1|Spirit_6</v>
+      <c r="N5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Monster_05</v>
-      </c>
-      <c r="B6" t="str">
-        <v>MonsterModel_05</v>
-      </c>
-      <c r="C6" t="str">
-        <v>石像鬼</v>
-      </c>
-      <c r="D6" t="str">
-        <v>PreferWarrior</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Ranged</v>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
       </c>
       <c r="F6">
         <v>240</v>
       </c>
       <c r="G6">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="H6">
         <v>16</v>
@@ -663,7 +1482,7 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>7.2</v>
+        <v>0.25</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -674,34 +1493,34 @@
       <c r="M6">
         <v>2.5</v>
       </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v>Iron_2|Spirit_9</v>
+      <c r="N6" t="s">
+        <v>20</v>
+      </c>
+      <c r="O6" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Monster_06</v>
-      </c>
-      <c r="B7" t="str">
-        <v>MonsterModel_06</v>
-      </c>
-      <c r="C7" t="str">
-        <v>巫妖徒</v>
-      </c>
-      <c r="D7" t="str">
-        <v>PreferProtagonist</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Melee</v>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
       </c>
       <c r="F7">
         <v>280</v>
       </c>
       <c r="G7">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="H7">
         <v>18</v>
@@ -710,7 +1529,7 @@
         <v>1.05</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="K7">
         <v>0.4</v>
@@ -721,34 +1540,34 @@
       <c r="M7">
         <v>0</v>
       </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v>Bone_1|Spirit_8</v>
+      <c r="N7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O7" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Monster_07</v>
-      </c>
-      <c r="B8" t="str">
-        <v>MonsterModel_07</v>
-      </c>
-      <c r="C8" t="str">
-        <v>骨龙幼崽</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Nearest</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Melee</v>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
       </c>
       <c r="F8">
         <v>320</v>
       </c>
       <c r="G8">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="H8">
         <v>20</v>
@@ -757,7 +1576,7 @@
         <v>1.1</v>
       </c>
       <c r="J8">
-        <v>2.1</v>
+        <v>0.25</v>
       </c>
       <c r="K8">
         <v>0.42</v>
@@ -768,34 +1587,34 @@
       <c r="M8">
         <v>0</v>
       </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v>Iron_1|Spirit_11</v>
+      <c r="N8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O8" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Monster_08</v>
-      </c>
-      <c r="B9" t="str">
-        <v>MonsterModel_08</v>
-      </c>
-      <c r="C9" t="str">
-        <v>血仆</v>
-      </c>
-      <c r="D9" t="str">
-        <v>PreferWarrior</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Ranged</v>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
       </c>
       <c r="F9">
         <v>360</v>
       </c>
       <c r="G9">
-        <v>3.9000000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="H9">
         <v>22</v>
@@ -804,7 +1623,7 @@
         <v>1.15</v>
       </c>
       <c r="J9">
-        <v>8.1</v>
+        <v>0.25</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -815,34 +1634,34 @@
       <c r="M9">
         <v>2.5</v>
       </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v>Bone_1|Spirit_10</v>
+      <c r="N9" t="s">
+        <v>20</v>
+      </c>
+      <c r="O9" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Monster_09</v>
-      </c>
-      <c r="B10" t="str">
-        <v>MonsterModel_09</v>
-      </c>
-      <c r="C10" t="str">
-        <v>暗影刺客</v>
-      </c>
-      <c r="D10" t="str">
-        <v>PreferProtagonist</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Melee</v>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
       </c>
       <c r="F10">
         <v>400</v>
       </c>
       <c r="G10">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="H10">
         <v>24</v>
@@ -851,7 +1670,7 @@
         <v>1.2</v>
       </c>
       <c r="J10">
-        <v>2.3</v>
+        <v>0.25</v>
       </c>
       <c r="K10">
         <v>0.46</v>
@@ -862,34 +1681,34 @@
       <c r="M10">
         <v>0</v>
       </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v>Iron_3|Spirit_13</v>
+      <c r="N10" t="s">
+        <v>20</v>
+      </c>
+      <c r="O10" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Monster_10</v>
-      </c>
-      <c r="B11" t="str">
-        <v>MonsterModel_10</v>
-      </c>
-      <c r="C11" t="str">
-        <v>巨型僵尸</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Nearest</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Melee</v>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
       </c>
       <c r="F11">
         <v>440</v>
       </c>
       <c r="G11">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="H11">
         <v>26</v>
@@ -898,7 +1717,7 @@
         <v>1.25</v>
       </c>
       <c r="J11">
-        <v>2.4</v>
+        <v>0.25</v>
       </c>
       <c r="K11">
         <v>0.48</v>
@@ -909,16 +1728,18 @@
       <c r="M11">
         <v>0</v>
       </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v>Bone_1|Spirit_12</v>
+      <c r="N11" t="s">
+        <v>20</v>
+      </c>
+      <c r="O11" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O11"/>
+    <ignoredError sqref="A1:O1 A2:F11 H2:I11 K2:O11" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="f:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07495F85-1EB0-4455-8241-4194649D7EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12280"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="128">
   <si>
     <t>怪物ID</t>
   </si>
@@ -199,7 +200,7 @@
     <t>Monster_01</t>
   </si>
   <si>
-    <t>MonsterModel_01</t>
+    <t>MonsterModel_05</t>
   </si>
   <si>
     <t>腐尸</t>
@@ -238,9 +239,6 @@
     <t>Monster_02</t>
   </si>
   <si>
-    <t>MonsterModel_02</t>
-  </si>
-  <si>
     <t>骷髅兵</t>
   </si>
   <si>
@@ -268,9 +266,6 @@
     <t>Monster_03</t>
   </si>
   <si>
-    <t>MonsterModel_03</t>
-  </si>
-  <si>
     <t>墓园犬</t>
   </si>
   <si>
@@ -292,9 +287,6 @@
     <t>Monster_04</t>
   </si>
   <si>
-    <t>MonsterModel_04</t>
-  </si>
-  <si>
     <t>幽魂</t>
   </si>
   <si>
@@ -313,9 +305,6 @@
     <t>Monster_05</t>
   </si>
   <si>
-    <t>MonsterModel_05</t>
-  </si>
-  <si>
     <t>石像鬼</t>
   </si>
   <si>
@@ -331,9 +320,6 @@
     <t>Monster_06</t>
   </si>
   <si>
-    <t>MonsterModel_06</t>
-  </si>
-  <si>
     <t>巫妖徒</t>
   </si>
   <si>
@@ -352,9 +338,6 @@
     <t>Monster_07</t>
   </si>
   <si>
-    <t>MonsterModel_07</t>
-  </si>
-  <si>
     <t>骨龙幼崽</t>
   </si>
   <si>
@@ -373,9 +356,6 @@
     <t>Monster_08</t>
   </si>
   <si>
-    <t>MonsterModel_08</t>
-  </si>
-  <si>
     <t>血仆</t>
   </si>
   <si>
@@ -394,9 +374,6 @@
     <t>Monster_09</t>
   </si>
   <si>
-    <t>MonsterModel_09</t>
-  </si>
-  <si>
     <t>暗影刺客</t>
   </si>
   <si>
@@ -415,9 +392,6 @@
     <t>Monster_10</t>
   </si>
   <si>
-    <t>MonsterModel_10</t>
-  </si>
-  <si>
     <t>巨型僵尸</t>
   </si>
   <si>
@@ -434,19 +408,22 @@
   </si>
   <si>
     <t>Bone_1|Spirit_12</t>
+  </si>
+  <si>
+    <t>朝向整圈翻转</t>
+  </si>
+  <si>
+    <t>0不转;1=(DirIndex+4)%8;缺省0</t>
+  </si>
+  <si>
+    <t>FacingYawFlip</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -455,151 +432,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -612,194 +452,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -807,311 +461,25 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1396,21 +764,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7545454545455" customWidth="1"/>
+    <col min="1" max="1" width="11.7265625" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1436,37 +804,40 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1492,37 +863,40 @@
         <v>25</v>
       </c>
       <c r="I2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>28</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>29</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>30</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>31</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>32</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>34</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:18">
+    <row r="3" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
@@ -1547,38 +921,41 @@
       <c r="H3" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -1601,54 +978,57 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I4">
-        <v>4000</v>
-      </c>
-      <c r="J4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
         <v>60</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>8</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>61</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>62</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>63</v>
       </c>
-      <c r="O4" t="s">
-        <v>64</v>
-      </c>
       <c r="P4" t="s">
         <v>64</v>
       </c>
       <c r="Q4" t="s">
+        <v>64</v>
+      </c>
+      <c r="R4" t="s">
         <v>65</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>67</v>
       </c>
       <c r="B5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" t="s">
         <v>68</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>69</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>70</v>
-      </c>
-      <c r="E5" t="s">
-        <v>71</v>
       </c>
       <c r="F5" t="s">
         <v>59</v>
@@ -1657,52 +1037,55 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I5">
-        <f>I4+500</f>
-        <v>4500</v>
-      </c>
-      <c r="J5" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <f>J4+30</f>
+        <v>55</v>
+      </c>
+      <c r="K5" t="s">
         <v>60</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M5" t="s">
         <v>72</v>
       </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
+        <v>62</v>
+      </c>
+      <c r="O5" t="s">
+        <v>64</v>
+      </c>
+      <c r="P5" t="s">
         <v>73</v>
       </c>
-      <c r="M5" t="s">
-        <v>62</v>
-      </c>
-      <c r="N5" t="s">
-        <v>64</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="Q5" t="s">
         <v>74</v>
       </c>
-      <c r="P5" t="s">
+      <c r="R5" t="s">
+        <v>65</v>
+      </c>
+      <c r="S5" t="s">
         <v>75</v>
       </c>
-      <c r="Q5" t="s">
-        <v>65</v>
-      </c>
-      <c r="R5" t="s">
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
         <v>77</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" t="s">
-        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>58</v>
@@ -1714,49 +1097,52 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I6">
-        <f t="shared" ref="I6:I13" si="0">I5+500</f>
-        <v>5000</v>
-      </c>
-      <c r="J6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <f t="shared" ref="J6:J13" si="0">J5+30</f>
+        <v>85</v>
+      </c>
+      <c r="K6" t="s">
         <v>60</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>79</v>
+      </c>
+      <c r="M6" t="s">
+        <v>80</v>
+      </c>
+      <c r="N6" t="s">
+        <v>62</v>
+      </c>
+      <c r="O6" t="s">
         <v>81</v>
       </c>
-      <c r="L6" t="s">
+      <c r="P6" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>64</v>
+      </c>
+      <c r="R6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S6" t="s">
         <v>82</v>
       </c>
-      <c r="M6" t="s">
-        <v>62</v>
-      </c>
-      <c r="N6" t="s">
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>83</v>
       </c>
-      <c r="O6" t="s">
-        <v>64</v>
-      </c>
-      <c r="P6" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>65</v>
-      </c>
-      <c r="R6" t="s">
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" t="s">
-        <v>87</v>
       </c>
       <c r="D7" t="s">
         <v>57</v>
@@ -1771,55 +1157,58 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <f t="shared" si="0"/>
-        <v>5500</v>
-      </c>
-      <c r="J7" t="s">
+        <v>115</v>
+      </c>
+      <c r="K7" t="s">
         <v>60</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
+        <v>85</v>
+      </c>
+      <c r="M7" t="s">
+        <v>86</v>
+      </c>
+      <c r="N7" t="s">
+        <v>62</v>
+      </c>
+      <c r="O7" t="s">
+        <v>87</v>
+      </c>
+      <c r="P7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>64</v>
+      </c>
+      <c r="R7" t="s">
+        <v>65</v>
+      </c>
+      <c r="S7" t="s">
         <v>88</v>
       </c>
-      <c r="L7" t="s">
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>89</v>
       </c>
-      <c r="M7" t="s">
-        <v>62</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" t="s">
         <v>90</v>
       </c>
-      <c r="O7" t="s">
-        <v>64</v>
-      </c>
-      <c r="P7" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>65</v>
-      </c>
-      <c r="R7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" t="s">
-        <v>94</v>
-      </c>
       <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" t="s">
         <v>70</v>
-      </c>
-      <c r="E8" t="s">
-        <v>71</v>
       </c>
       <c r="F8" t="s">
         <v>59</v>
@@ -1828,52 +1217,55 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
         <f t="shared" si="0"/>
-        <v>6000</v>
-      </c>
-      <c r="J8" t="s">
+        <v>145</v>
+      </c>
+      <c r="K8" t="s">
         <v>60</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>91</v>
+      </c>
+      <c r="M8" t="s">
+        <v>92</v>
+      </c>
+      <c r="N8" t="s">
+        <v>62</v>
+      </c>
+      <c r="O8" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>74</v>
+      </c>
+      <c r="R8" t="s">
+        <v>65</v>
+      </c>
+      <c r="S8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
         <v>95</v>
       </c>
-      <c r="L8" t="s">
-        <v>96</v>
-      </c>
-      <c r="M8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N8" t="s">
-        <v>64</v>
-      </c>
-      <c r="O8" t="s">
-        <v>88</v>
-      </c>
-      <c r="P8" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>65</v>
-      </c>
-      <c r="R8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" t="s">
-        <v>100</v>
-      </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>58</v>
@@ -1885,49 +1277,52 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
         <f t="shared" si="0"/>
-        <v>6500</v>
-      </c>
-      <c r="J9" t="s">
+        <v>175</v>
+      </c>
+      <c r="K9" t="s">
         <v>60</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
+        <v>96</v>
+      </c>
+      <c r="M9" t="s">
+        <v>97</v>
+      </c>
+      <c r="N9" t="s">
+        <v>62</v>
+      </c>
+      <c r="O9" t="s">
+        <v>98</v>
+      </c>
+      <c r="P9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>64</v>
+      </c>
+      <c r="R9" t="s">
+        <v>65</v>
+      </c>
+      <c r="S9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
         <v>101</v>
-      </c>
-      <c r="L9" t="s">
-        <v>102</v>
-      </c>
-      <c r="M9" t="s">
-        <v>62</v>
-      </c>
-      <c r="N9" t="s">
-        <v>103</v>
-      </c>
-      <c r="O9" t="s">
-        <v>64</v>
-      </c>
-      <c r="P9" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>65</v>
-      </c>
-      <c r="R9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" t="s">
-        <v>105</v>
-      </c>
-      <c r="B10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" t="s">
-        <v>107</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -1942,55 +1337,58 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
         <f t="shared" si="0"/>
-        <v>7000</v>
-      </c>
-      <c r="J10" t="s">
+        <v>205</v>
+      </c>
+      <c r="K10" t="s">
         <v>60</v>
       </c>
-      <c r="K10" t="s">
-        <v>108</v>
-      </c>
       <c r="L10" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M10" t="s">
+        <v>103</v>
+      </c>
+      <c r="N10" t="s">
         <v>62</v>
       </c>
-      <c r="N10" t="s">
-        <v>110</v>
-      </c>
       <c r="O10" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="P10" t="s">
         <v>64</v>
       </c>
       <c r="Q10" t="s">
+        <v>64</v>
+      </c>
+      <c r="R10" t="s">
         <v>65</v>
       </c>
-      <c r="R10" t="s">
-        <v>111</v>
+      <c r="S10" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s">
-        <v>113</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" t="s">
         <v>70</v>
-      </c>
-      <c r="E11" t="s">
-        <v>71</v>
       </c>
       <c r="F11" t="s">
         <v>59</v>
@@ -1999,52 +1397,55 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
         <f t="shared" si="0"/>
-        <v>7500</v>
-      </c>
-      <c r="J11" t="s">
+        <v>235</v>
+      </c>
+      <c r="K11" t="s">
         <v>60</v>
       </c>
-      <c r="K11" t="s">
-        <v>115</v>
-      </c>
       <c r="L11" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="M11" t="s">
+        <v>109</v>
+      </c>
+      <c r="N11" t="s">
         <v>62</v>
       </c>
-      <c r="N11" t="s">
-        <v>64</v>
-      </c>
       <c r="O11" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="Q11" t="s">
+        <v>74</v>
+      </c>
+      <c r="R11" t="s">
         <v>65</v>
       </c>
-      <c r="R11" t="s">
-        <v>118</v>
+      <c r="S11" t="s">
+        <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
         <v>58</v>
@@ -2056,49 +1457,52 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
         <f t="shared" si="0"/>
-        <v>8000</v>
-      </c>
-      <c r="J12" t="s">
+        <v>265</v>
+      </c>
+      <c r="K12" t="s">
         <v>60</v>
       </c>
-      <c r="K12" t="s">
-        <v>122</v>
-      </c>
       <c r="L12" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="M12" t="s">
+        <v>115</v>
+      </c>
+      <c r="N12" t="s">
         <v>62</v>
       </c>
-      <c r="N12" t="s">
-        <v>124</v>
-      </c>
       <c r="O12" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="P12" t="s">
         <v>64</v>
       </c>
       <c r="Q12" t="s">
+        <v>64</v>
+      </c>
+      <c r="R12" t="s">
         <v>65</v>
       </c>
-      <c r="R12" t="s">
-        <v>125</v>
+      <c r="S12" t="s">
+        <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B13" t="s">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
         <v>57</v>
@@ -2113,42 +1517,45 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
         <f t="shared" si="0"/>
-        <v>8500</v>
-      </c>
-      <c r="J13" t="s">
+        <v>295</v>
+      </c>
+      <c r="K13" t="s">
         <v>60</v>
       </c>
-      <c r="K13" t="s">
-        <v>129</v>
-      </c>
       <c r="L13" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="M13" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="N13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="O13" t="s">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="P13" t="s">
         <v>64</v>
       </c>
       <c r="Q13" t="s">
+        <v>64</v>
+      </c>
+      <c r="R13" t="s">
         <v>65</v>
       </c>
-      <c r="R13" t="s">
-        <v>133</v>
+      <c r="S13" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="f:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07495F85-1EB0-4455-8241-4194649D7EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="142">
   <si>
     <t>怪物ID</t>
   </si>
@@ -59,12 +58,27 @@
     <t>占地半径</t>
   </si>
   <si>
+    <t>推开系数</t>
+  </si>
+  <si>
+    <t>排斥强度系数</t>
+  </si>
+  <si>
+    <t>朝向整圈翻转</t>
+  </si>
+  <si>
     <t>怪物血量</t>
   </si>
   <si>
     <t>怪物移动速度</t>
   </si>
   <si>
+    <t>主动移动系数</t>
+  </si>
+  <si>
+    <t>被动移动系数</t>
+  </si>
+  <si>
     <t>怪物攻击力</t>
   </si>
   <si>
@@ -113,12 +127,27 @@
     <t>≥0；空→0.35；PushMap 刷出散开与 NavMeshAgent 避障半径</t>
   </si>
   <si>
+    <t>≥0；缺省 1；SoftCollision 排斥冲量缩放（邻域贡献×对方系数）；不改变占地圆</t>
+  </si>
+  <si>
+    <t>≥0；缺省 1；SoftCollision 单体排斥（有效=全局×本系数）；Register 注入</t>
+  </si>
+  <si>
+    <t>0不转;1=(DirIndex+4)%8;缺省0</t>
+  </si>
+  <si>
     <t>生成时初始化 maxHP / 当前 HP</t>
   </si>
   <si>
     <t>世界单位/秒或项目统一速度单位</t>
   </si>
   <si>
+    <t>≥0；ActiveChase 时×MoveSpeed；缺省1</t>
+  </si>
+  <si>
+    <t>≥0；PassiveChase 时×MoveSpeed；缺省1</t>
+  </si>
+  <si>
     <t>仅攻击士兵时用于伤害结算</t>
   </si>
   <si>
@@ -167,12 +196,27 @@
     <t>BodyRadius</t>
   </si>
   <si>
+    <t>PushCoefficient</t>
+  </si>
+  <si>
+    <t>RepulsionScale</t>
+  </si>
+  <si>
+    <t>FacingYawFlip</t>
+  </si>
+  <si>
     <t>MaxHP</t>
   </si>
   <si>
     <t>MoveSpeed</t>
   </si>
   <si>
+    <t>ActiveMoveMult</t>
+  </si>
+  <si>
+    <t>PassiveMoveMult</t>
+  </si>
+  <si>
     <t>AttackPower</t>
   </si>
   <si>
@@ -230,9 +274,6 @@
     <t>0</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Iron_1|Spirit_5</t>
   </si>
   <si>
@@ -410,20 +451,26 @@
     <t>Bone_1|Spirit_12</t>
   </si>
   <si>
-    <t>朝向整圈翻转</t>
-  </si>
-  <si>
-    <t>0不转;1=(DirIndex+4)%8;缺省0</t>
-  </si>
-  <si>
-    <t>FacingYawFlip</t>
+    <t>Monster_11</t>
+  </si>
+  <si>
+    <t>MonsterModel_06</t>
+  </si>
+  <si>
+    <t>骷髅猛士</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -432,14 +479,151 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -452,8 +636,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -461,25 +831,311 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -764,21 +1420,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:W14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.725" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="6" max="6" width="37" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -804,175 +1460,211 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>125</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="P2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Q2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="R2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="S2" t="s">
-        <v>35</v>
+        <v>41</v>
+      </c>
+      <c r="T2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W2" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" s="1" customFormat="1" spans="1:23">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="I3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
+      </c>
+      <c r="J3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" t="s">
+        <v>56</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
+      </c>
+      <c r="N3" t="s">
+        <v>59</v>
+      </c>
+      <c r="O3" t="s">
+        <v>60</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>53</v>
+        <v>64</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -981,57 +1673,66 @@
         <v>0.15</v>
       </c>
       <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>0.5</v>
+      </c>
+      <c r="K4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>25</v>
       </c>
-      <c r="K4" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4">
+      <c r="M4" t="s">
+        <v>75</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
         <v>8</v>
       </c>
-      <c r="M4" t="s">
-        <v>61</v>
-      </c>
-      <c r="N4" t="s">
-        <v>62</v>
-      </c>
-      <c r="O4" t="s">
-        <v>63</v>
-      </c>
-      <c r="P4" t="s">
-        <v>64</v>
-      </c>
       <c r="Q4" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="R4" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="S4" t="s">
-        <v>66</v>
+        <v>78</v>
+      </c>
+      <c r="T4" t="s">
+        <v>79</v>
+      </c>
+      <c r="U4" t="s">
+        <v>79</v>
+      </c>
+      <c r="W4" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1040,58 +1741,66 @@
         <v>0.15</v>
       </c>
       <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>0.5</v>
+      </c>
+      <c r="K5">
         <v>0</v>
       </c>
-      <c r="J5">
-        <f>J4+30</f>
+      <c r="L5">
         <v>55</v>
       </c>
-      <c r="K5" t="s">
-        <v>60</v>
-      </c>
-      <c r="L5" t="s">
-        <v>71</v>
-      </c>
       <c r="M5" t="s">
-        <v>72</v>
-      </c>
-      <c r="N5" t="s">
-        <v>62</v>
-      </c>
-      <c r="O5" t="s">
-        <v>64</v>
+        <v>75</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
       </c>
       <c r="P5" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>86</v>
+      </c>
+      <c r="R5" t="s">
+        <v>77</v>
+      </c>
+      <c r="S5" t="s">
+        <v>79</v>
+      </c>
+      <c r="T5" t="s">
+        <v>87</v>
+      </c>
+      <c r="U5" t="s">
+        <v>88</v>
+      </c>
+      <c r="W5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" t="s">
         <v>73</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="F6" t="s">
         <v>74</v>
-      </c>
-      <c r="R5" t="s">
-        <v>65</v>
-      </c>
-      <c r="S5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" t="s">
-        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -1100,58 +1809,66 @@
         <v>0.15</v>
       </c>
       <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0.5</v>
+      </c>
+      <c r="K6">
         <v>0</v>
       </c>
-      <c r="J6">
-        <f t="shared" ref="J6:J13" si="0">J5+30</f>
+      <c r="L6">
         <v>85</v>
       </c>
-      <c r="K6" t="s">
-        <v>60</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
+        <v>75</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>94</v>
+      </c>
+      <c r="R6" t="s">
+        <v>77</v>
+      </c>
+      <c r="S6" t="s">
+        <v>95</v>
+      </c>
+      <c r="T6" t="s">
         <v>79</v>
       </c>
-      <c r="M6" t="s">
-        <v>80</v>
-      </c>
-      <c r="N6" t="s">
-        <v>62</v>
-      </c>
-      <c r="O6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P6" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>64</v>
-      </c>
-      <c r="R6" t="s">
-        <v>65</v>
-      </c>
-      <c r="S6" t="s">
-        <v>82</v>
+      <c r="U6" t="s">
+        <v>79</v>
+      </c>
+      <c r="W6" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -1160,58 +1877,66 @@
         <v>0.15</v>
       </c>
       <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0.5</v>
+      </c>
+      <c r="K7">
         <v>0</v>
       </c>
-      <c r="J7">
-        <f t="shared" si="0"/>
+      <c r="L7">
         <v>115</v>
       </c>
-      <c r="K7" t="s">
-        <v>60</v>
-      </c>
-      <c r="L7" t="s">
-        <v>85</v>
-      </c>
       <c r="M7" t="s">
-        <v>86</v>
-      </c>
-      <c r="N7" t="s">
-        <v>62</v>
-      </c>
-      <c r="O7" t="s">
-        <v>87</v>
+        <v>75</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="Q7" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="R7" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="S7" t="s">
-        <v>88</v>
+        <v>101</v>
+      </c>
+      <c r="T7" t="s">
+        <v>79</v>
+      </c>
+      <c r="U7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W7" t="s">
+        <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -1220,58 +1945,66 @@
         <v>0.15</v>
       </c>
       <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0.5</v>
+      </c>
+      <c r="K8">
         <v>0</v>
       </c>
-      <c r="J8">
-        <f t="shared" si="0"/>
+      <c r="L8">
         <v>145</v>
       </c>
-      <c r="K8" t="s">
-        <v>60</v>
-      </c>
-      <c r="L8" t="s">
-        <v>91</v>
-      </c>
       <c r="M8" t="s">
+        <v>75</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>106</v>
+      </c>
+      <c r="R8" t="s">
+        <v>77</v>
+      </c>
+      <c r="S8" t="s">
+        <v>79</v>
+      </c>
+      <c r="T8" t="s">
+        <v>99</v>
+      </c>
+      <c r="U8" t="s">
+        <v>88</v>
+      </c>
+      <c r="W8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" t="s">
         <v>92</v>
       </c>
-      <c r="N8" t="s">
-        <v>62</v>
-      </c>
-      <c r="O8" t="s">
-        <v>64</v>
-      </c>
-      <c r="P8" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q8" t="s">
+      <c r="E9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" t="s">
         <v>74</v>
-      </c>
-      <c r="R8" t="s">
-        <v>65</v>
-      </c>
-      <c r="S8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -1280,58 +2013,66 @@
         <v>0.15</v>
       </c>
       <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>0.5</v>
+      </c>
+      <c r="K9">
         <v>0</v>
       </c>
-      <c r="J9">
-        <f t="shared" si="0"/>
+      <c r="L9">
         <v>175</v>
       </c>
-      <c r="K9" t="s">
-        <v>60</v>
-      </c>
-      <c r="L9" t="s">
-        <v>96</v>
-      </c>
       <c r="M9" t="s">
-        <v>97</v>
-      </c>
-      <c r="N9" t="s">
-        <v>62</v>
-      </c>
-      <c r="O9" t="s">
-        <v>98</v>
+        <v>75</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="Q9" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="R9" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="S9" t="s">
-        <v>99</v>
+        <v>112</v>
+      </c>
+      <c r="T9" t="s">
+        <v>79</v>
+      </c>
+      <c r="U9" t="s">
+        <v>79</v>
+      </c>
+      <c r="W9" t="s">
+        <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23">
       <c r="A10" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -1340,58 +2081,66 @@
         <v>0.15</v>
       </c>
       <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0.5</v>
+      </c>
+      <c r="K10">
         <v>0</v>
       </c>
-      <c r="J10">
-        <f t="shared" si="0"/>
+      <c r="L10">
         <v>205</v>
       </c>
-      <c r="K10" t="s">
-        <v>60</v>
-      </c>
-      <c r="L10" t="s">
-        <v>102</v>
-      </c>
       <c r="M10" t="s">
-        <v>103</v>
-      </c>
-      <c r="N10" t="s">
-        <v>62</v>
-      </c>
-      <c r="O10" t="s">
-        <v>104</v>
+        <v>75</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="Q10" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="R10" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="S10" t="s">
-        <v>105</v>
+        <v>118</v>
+      </c>
+      <c r="T10" t="s">
+        <v>79</v>
+      </c>
+      <c r="U10" t="s">
+        <v>79</v>
+      </c>
+      <c r="W10" t="s">
+        <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -1400,58 +2149,66 @@
         <v>0.15</v>
       </c>
       <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>0.5</v>
+      </c>
+      <c r="K11">
         <v>0</v>
       </c>
-      <c r="J11">
-        <f t="shared" si="0"/>
+      <c r="L11">
         <v>235</v>
       </c>
-      <c r="K11" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11" t="s">
-        <v>108</v>
-      </c>
       <c r="M11" t="s">
-        <v>109</v>
-      </c>
-      <c r="N11" t="s">
-        <v>62</v>
-      </c>
-      <c r="O11" t="s">
-        <v>64</v>
+        <v>75</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="Q11" t="s">
+        <v>123</v>
+      </c>
+      <c r="R11" t="s">
+        <v>77</v>
+      </c>
+      <c r="S11" t="s">
+        <v>79</v>
+      </c>
+      <c r="T11" t="s">
+        <v>124</v>
+      </c>
+      <c r="U11" t="s">
+        <v>88</v>
+      </c>
+      <c r="W11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" t="s">
         <v>74</v>
-      </c>
-      <c r="R11" t="s">
-        <v>65</v>
-      </c>
-      <c r="S11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -1460,58 +2217,66 @@
         <v>0.15</v>
       </c>
       <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0.5</v>
+      </c>
+      <c r="K12">
         <v>0</v>
       </c>
-      <c r="J12">
-        <f t="shared" si="0"/>
+      <c r="L12">
         <v>265</v>
       </c>
-      <c r="K12" t="s">
-        <v>60</v>
-      </c>
-      <c r="L12" t="s">
-        <v>114</v>
-      </c>
       <c r="M12" t="s">
-        <v>115</v>
-      </c>
-      <c r="N12" t="s">
-        <v>62</v>
-      </c>
-      <c r="O12" t="s">
-        <v>116</v>
+        <v>75</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="Q12" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="R12" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="S12" t="s">
-        <v>117</v>
+        <v>130</v>
+      </c>
+      <c r="T12" t="s">
+        <v>79</v>
+      </c>
+      <c r="U12" t="s">
+        <v>79</v>
+      </c>
+      <c r="W12" t="s">
+        <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -1520,42 +2285,118 @@
         <v>0.15</v>
       </c>
       <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>0.5</v>
+      </c>
+      <c r="K13">
         <v>0</v>
       </c>
-      <c r="J13">
-        <f t="shared" si="0"/>
+      <c r="L13">
         <v>295</v>
       </c>
-      <c r="K13" t="s">
-        <v>60</v>
-      </c>
-      <c r="L13" t="s">
-        <v>120</v>
-      </c>
       <c r="M13" t="s">
-        <v>121</v>
-      </c>
-      <c r="N13" t="s">
-        <v>122</v>
-      </c>
-      <c r="O13" t="s">
-        <v>123</v>
+        <v>75</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="Q13" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="R13" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="S13" t="s">
-        <v>124</v>
+        <v>137</v>
+      </c>
+      <c r="T13" t="s">
+        <v>79</v>
+      </c>
+      <c r="U13" t="s">
+        <v>79</v>
+      </c>
+      <c r="W13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+      <c r="H14">
+        <v>0.3</v>
+      </c>
+      <c r="I14">
+        <v>1.5</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>10000</v>
+      </c>
+      <c r="M14">
+        <v>0.3</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1500</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>135</v>
+      </c>
+      <c r="R14">
+        <v>0.45</v>
+      </c>
+      <c r="S14">
+        <v>1.25</v>
+      </c>
+      <c r="T14" t="s">
+        <v>79</v>
+      </c>
+      <c r="U14" t="s">
+        <v>79</v>
+      </c>
+      <c r="W14" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
@@ -1505,7 +1505,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Iron_1|Spirit_5</t>
+          <t>Iron;1|Spirit;5</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Bone_1|Spirit_4</t>
+          <t>Bone;1|Spirit;4</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Iron_3|Spirit_7</t>
+          <t>Iron;3|Spirit;7</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Bone_1|Spirit_6</t>
+          <t>Bone;1|Spirit;6</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Iron_2|Spirit_9</t>
+          <t>Iron;2|Spirit;9</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Bone_1|Spirit_8</t>
+          <t>Bone;1|Spirit;8</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Iron_1|Spirit_11</t>
+          <t>Iron;1|Spirit;11</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Bone_1|Spirit_10</t>
+          <t>Bone;1|Spirit;10</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Iron_3|Spirit_13</t>
+          <t>Iron;3|Spirit;13</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Bone_1|Spirit_12</t>
+          <t>Bone;1|Spirit;12</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Bone_1|Spirit_12</t>
+          <t>Bone;1|Spirit;12</t>
         </is>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
@@ -2,374 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="1">
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -377,306 +42,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1029,6 +403,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1038,13 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <cols>
-    <col width="11.725" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-  </cols>
+  <dimension ref="A1:AC14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1114,55 +484,80 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>怪物移动速度</t>
+          <t>怪物走速度</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>主动移动系数</t>
+          <t>怪物跑速度</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>被动移动系数</t>
+          <t>走转跑时间</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>主动追击移速倍率</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>被动追击移速倍率</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>怪物攻击力</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>攻击速度</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>攻击距离</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>近战前摇</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>远程弹速</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>远程超时</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>怪物技能</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>普通攻击动作调用</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>走</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>跑</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
         <is>
           <t>怪物掉落</t>
         </is>
@@ -1196,7 +591,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1=普通(Normal) / 2=精英(Elite) / 3=BOSS(Boss)；缺列或空→1；非法→加载失败；异于 PushMapSpawnConfig.IsBoss；本批不驱动技能</t>
+          <t>1=普通/2=精英/3=BOSS；空→1；非法失败；异于 PushMap IsBoss</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1216,12 +611,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>≥0；缺省 1；SoftCollision 排斥冲量缩放（邻域贡献×对方系数）；不改变占地圆</t>
+          <t>≥0；缺省1；SoftCollision 排斥冲量缩放（邻域贡献×对方系数）；不改占地圆</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>≥0；缺省 1；SoftCollision 单体排斥（有效=全局×本系数）；Register 注入</t>
+          <t>≥0；缺省1；SoftCollision 单体排斥（有效=全局×本系数）</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1236,82 +631,107 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>世界单位/秒或项目统一速度单位</t>
+          <t>世界单位/秒；走态移速</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>≥0；ActiveChase 时×MoveSpeed；缺省1</t>
+          <t>世界单位/秒；缺/≤0→回退 MoveSpeed</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>≥0；PassiveChase 时×MoveSpeed；缺省1</t>
+          <t>秒；持续移动达到后切跑；缺→0.5；0=一开跑</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>ActiveChase 时×当前 gait 移速；缺→1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>PassiveChase 时×当前 gait 移速；缺→1</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>仅攻击士兵时用于伤害结算</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>攻击频率</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>进入攻击态距离</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>≥0 秒；Melee 时用</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>≥0；Ranged 时用</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>≥0 秒；超时未命中→未命中</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>SkillId_CdSeconds|…；Demo v1 不施放</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>击杀产出；编码同 Dig LootDrop</t>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>SkillId;CdSeconds|…；禁止用 _ 后缀表示 CD</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>基名|基名|…；每次 PlayAttack 随机；空→Attack1</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>BlendTree 状态名|…；Bind/复活完成各抽一次；空→WalkBT</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>BlendTree 状态名|…；与走同生命周期；跑态移动时播</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>击杀产出；编码 Id;Count|Id;Count|…</t>
         </is>
       </c>
     </row>
-    <row r="3" customFormat="1" s="1">
-      <c r="A3" s="1" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>MonsterId</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ModelId</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>DisplayName</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TargetSelect</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>AttackMode</t>
         </is>
@@ -1321,12 +741,12 @@
           <t>MonsterType</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>AggroMode</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>AlertRadius</t>
         </is>
@@ -1351,62 +771,87 @@
           <t>FacingYawFlip</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>MaxHP</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>MoveSpeed</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>RunSpeed</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>WalkToRunSeconds</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>ActiveMoveMult</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>PassiveMoveMult</t>
         </is>
       </c>
-      <c r="Q3" s="1" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>AttackPower</t>
         </is>
       </c>
-      <c r="R3" s="1" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>AttackSpeed</t>
         </is>
       </c>
-      <c r="S3" s="1" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>AttackRange</t>
         </is>
       </c>
-      <c r="T3" s="1" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>MeleeWindupSeconds</t>
         </is>
       </c>
-      <c r="U3" s="1" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>RangedProjectileSpeed</t>
         </is>
       </c>
-      <c r="V3" s="1" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>RangedTimeoutSeconds</t>
         </is>
       </c>
-      <c r="W3" s="1" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Skills</t>
         </is>
       </c>
-      <c r="X3" s="1" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>NormalAttackAnims</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>WalkAnims</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>RunAnims</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>LootDrop</t>
         </is>
@@ -1438,72 +883,107 @@
           <t>Melee</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>ActiveChase</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>25</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>8</v>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>MSkill_SelfRevive;0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Iron;1|Spirit;5</t>
         </is>
@@ -1535,74 +1015,102 @@
           <t>Ranged</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>ActiveChase</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>55</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Bone;1|Spirit;4</t>
         </is>
@@ -1634,74 +1142,102 @@
           <t>Melee</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>ActiveChase</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>85</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>0.34</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Iron;3|Spirit;7</t>
         </is>
@@ -1733,74 +1269,102 @@
           <t>Melee</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>ActiveChase</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>115</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>0.36</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Bone;1|Spirit;6</t>
         </is>
@@ -1832,74 +1396,102 @@
           <t>Ranged</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>ActiveChase</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>145</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>Iron;2|Spirit;9</t>
         </is>
@@ -1931,74 +1523,102 @@
           <t>Melee</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>ActiveChase</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>175</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>Bone;1|Spirit;8</t>
         </is>
@@ -2030,74 +1650,102 @@
           <t>Melee</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>ActiveChase</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>205</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>Iron;1|Spirit;11</t>
         </is>
@@ -2129,74 +1777,102 @@
           <t>Ranged</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>ActiveChase</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>235</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>Bone;1|Spirit;10</t>
         </is>
@@ -2228,74 +1904,102 @@
           <t>Melee</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>ActiveChase</t>
         </is>
       </c>
-      <c r="H12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>265</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>0.46</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>Iron;3|Spirit;13</t>
         </is>
@@ -2327,74 +2031,102 @@
           <t>Melee</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>1</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>ActiveChase</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>5</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>295</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>Bone;1|Spirit;12</t>
         </is>
@@ -2426,66 +2158,102 @@
           <t>Melee</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>3</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>ActiveChase</t>
         </is>
       </c>
-      <c r="H14" t="n">
-        <v>10</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>10000</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1500</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="S14" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>Bone;1|Spirit;12</t>
         </is>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
@@ -997,7 +997,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MonsterModel_05</t>
+          <t>MonsterModel_02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MonsterModel_05</t>
+          <t>MonsterModel_04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MonsterModel_05</t>
+          <t>MonsterModel_07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">

--- a/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AD14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,11 @@
           <t>怪物掉落</t>
         </is>
       </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>士兵简画图标</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -709,6 +714,11 @@
           <t>击杀产出；编码 Id;Count|Id;Count|…</t>
         </is>
       </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>UI-033 战斗指示器简画；仅文件名；Resources/UI/Icons/{Id}；空=空框</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -856,6 +866,11 @@
           <t>LootDrop</t>
         </is>
       </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>SilhouetteIconAssetId</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -988,6 +1003,7 @@
           <t>Iron;1|Spirit;5</t>
         </is>
       </c>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1115,6 +1131,7 @@
           <t>Bone;1|Spirit;4</t>
         </is>
       </c>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1242,6 +1259,7 @@
           <t>Iron;3|Spirit;7</t>
         </is>
       </c>
+      <c r="AD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1369,6 +1387,7 @@
           <t>Bone;1|Spirit;6</t>
         </is>
       </c>
+      <c r="AD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1496,6 +1515,7 @@
           <t>Iron;2|Spirit;9</t>
         </is>
       </c>
+      <c r="AD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1623,6 +1643,7 @@
           <t>Bone;1|Spirit;8</t>
         </is>
       </c>
+      <c r="AD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1750,6 +1771,7 @@
           <t>Iron;1|Spirit;11</t>
         </is>
       </c>
+      <c r="AD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1877,6 +1899,7 @@
           <t>Bone;1|Spirit;10</t>
         </is>
       </c>
+      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2004,6 +2027,7 @@
           <t>Iron;3|Spirit;13</t>
         </is>
       </c>
+      <c r="AD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2131,6 +2155,7 @@
           <t>Bone;1|Spirit;12</t>
         </is>
       </c>
+      <c r="AD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2258,6 +2283,7 @@
           <t>Bone;1|Spirit;12</t>
         </is>
       </c>
+      <c r="AD14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
